--- a/assets/test_corpus/seeded_defects/seeded-defects.xlsx
+++ b/assets/test_corpus/seeded_defects/seeded-defects.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -606,22 +606,22 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Subtotal</t>
-        </is>
-      </c>
-      <c r="B16">
-        <f>SUM(B15:B15)</f>
-        <v/>
+          <t>Component B</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Component B</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>7</v>
+          <t>Subtotal</t>
+        </is>
+      </c>
+      <c r="B17">
+        <f>SUM(B15:B15)</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -744,6 +744,9 @@
           <t>SKU1</t>
         </is>
       </c>
+      <c r="B37" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -751,12 +754,35 @@
           <t xml:space="preserve"> sku1 </t>
         </is>
       </c>
+      <c r="B38" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Lookup</t>
+        </is>
+      </c>
+      <c r="B39">
+        <f>VLOOKUP("SKU1",A37:B38,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Merged region</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Merged note</t>
-        </is>
+      <c r="A42" t="n">
+        <v>100</v>
+      </c>
+      <c r="C42">
+        <f>SUM(A42:B42)</f>
+        <v/>
       </c>
     </row>
     <row r="44">

--- a/assets/test_corpus/seeded_defects/seeded-defects.xlsx
+++ b/assets/test_corpus/seeded_defects/seeded-defects.xlsx
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B27">
-        <f>IFERROR(B2/B99,"")</f>
+        <f>IFERROR(B2/B99,0)</f>
         <v/>
       </c>
     </row>
